--- a/YSIG/Stock Pitch/RBLX/Pitch Deck Round One/Spreadsheets/RBLX Analysis.xlsx
+++ b/YSIG/Stock Pitch/RBLX/Pitch Deck Round One/Spreadsheets/RBLX Analysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mateo/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mateo/Documents/Notes/YSIG/Stock Pitch/RBLX/Pitch Deck Round One/Spreadsheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A748AC73-7403-2245-A830-45691D235D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2FE5B5-0289-EF4C-99CD-9192A3F8680A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20160" activeTab="1" xr2:uid="{F0B47FEF-7E4B-0F45-8E5F-95A1124C315F}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20160" activeTab="4" xr2:uid="{F0B47FEF-7E4B-0F45-8E5F-95A1124C315F}"/>
   </bookViews>
   <sheets>
     <sheet name="DAU" sheetId="1" r:id="rId1"/>
@@ -20,11 +20,9 @@
     <sheet name="BOOKINGS TO REVENUE" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">REVENUE!$B$3:$B$6</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">REVENUE!$K$2</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">REVENUE!$K$3:$K$6</definedName>
+    <definedName name="___thinkcellN6LAAAAAAAAAAAABAAAIJZXZSKNKR4KNGOZPGV2M3RFRI" localSheetId="4" hidden="1">'BOOKINGS TO REVENUE'!$B$9:$K$10</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -187,55 +185,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="14">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF156082"/>
-          <bgColor rgb="FF156082"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -527,6 +483,48 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF156082"/>
+          <bgColor rgb="FF156082"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
@@ -722,36 +720,36 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>DAU!$C$3:$K$3</c:f>
+              <c:f>ABPDAU!$C$3:$K$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>15.7</c:v>
+                  <c:v>33.53</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15.6</c:v>
+                  <c:v>46.56</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>16.2</c:v>
+                  <c:v>33.950000000000003</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>17.100000000000001</c:v>
+                  <c:v>34.36</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>19.7</c:v>
+                  <c:v>35.51</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>18</c:v>
+                  <c:v>47.79</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>19.7</c:v>
+                  <c:v>36.46</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>20.6</c:v>
+                  <c:v>40.69</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>26.1</c:v>
+                  <c:v>40.18</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -815,36 +813,36 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ABPDAU!$C$3:$K$3</c:f>
+              <c:f>DAU!$C$3:$K$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>33.53</c:v>
+                  <c:v>15.7</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46.56</c:v>
+                  <c:v>15.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>33.950000000000003</c:v>
+                  <c:v>16.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>34.36</c:v>
+                  <c:v>17.100000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>35.51</c:v>
+                  <c:v>19.7</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>47.79</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>36.46</c:v>
+                  <c:v>19.7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>40.69</c:v>
+                  <c:v>20.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>40.18</c:v>
+                  <c:v>26.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10313,35 +10311,35 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{07CA30B0-1C03-E14D-9136-905283E1C827}" name="RBLX_Percent_Difference_Bookings_Revenue" displayName="RBLX_Percent_Difference_Bookings_Revenue" ref="B9:K13" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{07CA30B0-1C03-E14D-9136-905283E1C827}" name="RBLX_Percent_Difference_Bookings_Revenue" displayName="RBLX_Percent_Difference_Bookings_Revenue" ref="B9:K13" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11" tableBorderDxfId="10">
   <autoFilter ref="B9:K13" xr:uid="{07CA30B0-1C03-E14D-9136-905283E1C827}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{7BF6487C-168D-1441-B7EA-25C16AD32EE0}" name="REGION" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{900BA925-36CC-394C-B8A0-1A7CA9524174}" name="2023 Q3" dataDxfId="10">
+    <tableColumn id="1" xr3:uid="{7BF6487C-168D-1441-B7EA-25C16AD32EE0}" name="REGION" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{900BA925-36CC-394C-B8A0-1A7CA9524174}" name="2023 Q3" dataDxfId="8">
       <calculatedColumnFormula>C3/BOOKINGS!C3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{D3EEDF46-1C25-2E4C-89B8-23C12CE41C33}" name="2023 Q4" dataDxfId="9">
+    <tableColumn id="3" xr3:uid="{D3EEDF46-1C25-2E4C-89B8-23C12CE41C33}" name="2023 Q4" dataDxfId="7">
       <calculatedColumnFormula>D3/BOOKINGS!D3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E2B3C0F5-2AEF-4C4B-8950-D83EE359CD0B}" name="2024 Q1" dataDxfId="8">
+    <tableColumn id="4" xr3:uid="{E2B3C0F5-2AEF-4C4B-8950-D83EE359CD0B}" name="2024 Q1" dataDxfId="6">
       <calculatedColumnFormula>E3/BOOKINGS!E3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{E1C3E5BB-3CF8-3B46-87A4-315E7114F71A}" name="2024 Q2" dataDxfId="7">
+    <tableColumn id="5" xr3:uid="{E1C3E5BB-3CF8-3B46-87A4-315E7114F71A}" name="2024 Q2" dataDxfId="5">
       <calculatedColumnFormula>F3/BOOKINGS!F3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{C150596C-8AD3-6243-9B7E-9BA45916E3F5}" name="2024 Q3" dataDxfId="6">
+    <tableColumn id="6" xr3:uid="{C150596C-8AD3-6243-9B7E-9BA45916E3F5}" name="2024 Q3" dataDxfId="4">
       <calculatedColumnFormula>G3/BOOKINGS!G3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3153E010-23EB-C148-B23D-BFFD9C3F1729}" name="2024 Q4" dataDxfId="5">
+    <tableColumn id="7" xr3:uid="{3153E010-23EB-C148-B23D-BFFD9C3F1729}" name="2024 Q4" dataDxfId="3">
       <calculatedColumnFormula>H3/BOOKINGS!H3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{5F5A058B-09FF-DC4B-91CC-82F652A77FC3}" name="2025 Q1" dataDxfId="4">
+    <tableColumn id="8" xr3:uid="{5F5A058B-09FF-DC4B-91CC-82F652A77FC3}" name="2025 Q1" dataDxfId="2">
       <calculatedColumnFormula>I3/BOOKINGS!I3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{AFB531A4-649F-9A40-BD9F-FC2AC8257FB9}" name="2025 Q2" dataDxfId="3">
+    <tableColumn id="9" xr3:uid="{AFB531A4-649F-9A40-BD9F-FC2AC8257FB9}" name="2025 Q2" dataDxfId="1">
       <calculatedColumnFormula>J3/BOOKINGS!J3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{4D11DCDB-47A1-1147-8280-4AF886A1E345}" name="2025 Q3" dataDxfId="2">
+    <tableColumn id="10" xr3:uid="{4D11DCDB-47A1-1147-8280-4AF886A1E345}" name="2025 Q3" dataDxfId="0">
       <calculatedColumnFormula>K3/BOOKINGS!K3</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10882,6 +10880,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE507D9D-D856-2D4F-9DE1-CD93FBDBE7E2}">
   <dimension ref="B2:K7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="26" max="26" width="12" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
@@ -11532,7 +11533,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE84548-AC1C-7A4D-99F8-030DCB120806}">
-  <dimension ref="B2:K13"/>
+  <dimension ref="B2:K15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
@@ -11924,6 +11925,35 @@
       </c>
       <c r="K13" s="2">
         <f>K6/BOOKINGS!K6</f>
+        <v>-0.43315266485998194</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C15">
+        <v>-0.25320056899004262</v>
+      </c>
+      <c r="D15">
+        <v>-0.35225955967555039</v>
+      </c>
+      <c r="E15">
+        <v>-0.29268292682926828</v>
+      </c>
+      <c r="F15">
+        <v>-0.16525934861278652</v>
+      </c>
+      <c r="G15">
+        <v>-0.24819027921406411</v>
+      </c>
+      <c r="H15">
+        <v>-0.26026119402985082</v>
+      </c>
+      <c r="I15">
+        <v>-0.2477954144620812</v>
+      </c>
+      <c r="J15">
+        <v>-0.29526029526029518</v>
+      </c>
+      <c r="K15">
         <v>-0.43315266485998194</v>
       </c>
     </row>
